--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_023.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_023.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="166">
   <si>
     <t>Sezione</t>
   </si>
@@ -465,6 +465,21 @@
   </si>
   <si>
     <t>evento.eventoCollegato</t>
+  </si>
+  <si>
+    <t>Soggetto intervenuto</t>
+  </si>
+  <si>
+    <t>evento.interprete</t>
+  </si>
+  <si>
+    <t>195,196</t>
+  </si>
+  <si>
+    <t>evento.ausilioInterprete,!=,true &amp;&amp; evento.ausilioInterprete,!=,S &amp;&amp; evento.ausilioInterprete,!=,SI</t>
+  </si>
+  <si>
+    <t>Firmatario</t>
   </si>
   <si>
     <t>Dettaglio evento</t>
@@ -553,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.06640625" customWidth="true" bestFit="true"/>
@@ -562,7 +577,7 @@
     <col min="4" max="4" width="31.90234375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="50.08203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="89.16796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4457,22 +4472,22 @@
         <v>151</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D170" s="2" t="s">
+      <c r="E170" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F170" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E170" s="2" t="s">
+      <c r="G170" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="171">
@@ -4480,22 +4495,22 @@
         <v>151</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="172">
@@ -4503,22 +4518,22 @@
         <v>151</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>157</v>
+        <v>51</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>158</v>
+        <v>52</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="173">
@@ -4526,21 +4541,665 @@
         <v>151</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C173" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D173" s="2" t="s">
+      <c r="F198" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E173" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G173" s="2" t="s">
+      <c r="E201" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="2" t="s">
         <v>29</v>
       </c>
     </row>
